--- a/coronavirus_response_forms/023_covid_19_workplace_safety_checklist_form--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/023_covid_19_workplace_safety_checklist_form--coronavirus_response_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'under_100.4°f_(under_38°c)'}</t>
+          <t>under_100.4°f_(under_38°c)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Under 100.4°F (Under 38°C)'}</t>
+          <t>Under 100.4°F (Under 38°C)</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'100.4°f_or_higher_(38°c_or_higher)'}</t>
+          <t>100.4°f_or_higher_(38°c_or_higher)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '100.4°F or higher (38°C or higher)'}</t>
+          <t>100.4°F or higher (38°C or higher)</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'maintaining_6_feet_distance'}</t>
+          <t>maintaining_6_feet_distance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Maintaining 6 feet distance'}</t>
+          <t>Maintaining 6 feet distance</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_maintaining_6_feet_distance'}</t>
+          <t>not_maintaining_6_feet_distance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not maintaining 6 feet distance'}</t>
+          <t>Not maintaining 6 feet distance</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'wearing_hand_sanitizer'}</t>
+          <t>wearing_hand_sanitizer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Wearing hand sanitizer'}</t>
+          <t>Wearing hand sanitizer</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'not_wearing_hand_sanitizer'}</t>
+          <t>not_wearing_hand_sanitizer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Not wearing hand sanitizer'}</t>
+          <t>Not wearing hand sanitizer</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'fever'}</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Fever'}</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'cough'}</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Cough'}</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'sore_throat'}</t>
+          <t>sore_throat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Sore throat'}</t>
+          <t>Sore throat</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'no_contact'}</t>
+          <t>no_contact</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'No contact'}</t>
+          <t>No contact</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'exposed_to_someone_with_covid-19'}</t>
+          <t>exposed_to_someone_with_covid-19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Exposed to someone with COVID-19'}</t>
+          <t>Exposed to someone with COVID-19</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'exposed_to_someone_with_a_high_risk_behavior'}</t>
+          <t>exposed_to_someone_with_a_high_risk_behavior</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Exposed to someone with a high risk behavior'}</t>
+          <t>Exposed to someone with a high risk behavior</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'fully_vaccinated'}</t>
+          <t>fully_vaccinated</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Fully vaccinated'}</t>
+          <t>Fully vaccinated</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'partly_vaccinated'}</t>
+          <t>partly_vaccinated</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Partly vaccinated'}</t>
+          <t>Partly vaccinated</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'not_vaccinated'}</t>
+          <t>not_vaccinated</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Not vaccinated'}</t>
+          <t>Not vaccinated</t>
         </is>
       </c>
     </row>
